--- a/study_case_model/scenario_variables/other_experiment_data/demand_scenarios135.xlsx
+++ b/study_case_model/scenario_variables/other_experiment_data/demand_scenarios135.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,27 +417,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>stage</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>scenario_index</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>node</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>supplier</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>demand</t>
         </is>
@@ -473,7 +461,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29663.57471662897</v>
+        <v>27107.43900801275</v>
       </c>
     </row>
     <row r="3">
@@ -536,7 +524,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>13223.31460082158</v>
+        <v>20329.75360134555</v>
       </c>
     </row>
     <row r="6">
@@ -599,7 +587,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>9773.235590656743</v>
+        <v>11719.54156116022</v>
       </c>
     </row>
     <row r="9">
@@ -662,7 +650,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>18514.88818669097</v>
+        <v>17041.994392047</v>
       </c>
     </row>
     <row r="12">
@@ -704,7 +692,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4628.722046672743</v>
+        <v>4260.498598011751</v>
       </c>
     </row>
     <row r="14">
@@ -725,7 +713,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>48883.49856349931</v>
+        <v>41159.52864583683</v>
       </c>
     </row>
     <row r="15">
@@ -788,7 +776,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14827.52036581504</v>
+        <v>15686.00786382884</v>
       </c>
     </row>
     <row r="18">
@@ -851,7 +839,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>26332.75750699941</v>
+        <v>27677.61614473785</v>
       </c>
     </row>
     <row r="21">
@@ -914,7 +902,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>14984.91730967424</v>
+        <v>19803.17803554509</v>
       </c>
     </row>
     <row r="24">
@@ -977,7 +965,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>13925.74194127236</v>
+        <v>15873.49953287469</v>
       </c>
     </row>
     <row r="27">
@@ -1040,7 +1028,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>23663.51447170294</v>
+        <v>21843.79712525966</v>
       </c>
     </row>
     <row r="30">
@@ -1082,7 +1070,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5915.878617925736</v>
+        <v>5460.949281314915</v>
       </c>
     </row>
     <row r="32">
@@ -1103,7 +1091,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>58396.8567189656</v>
+        <v>62192.9317825844</v>
       </c>
     </row>
     <row r="33">
@@ -1166,7 +1154,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>16552.92772082983</v>
+        <v>14861.10815721355</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1217,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>31254.41615911678</v>
+        <v>18782.53741808446</v>
       </c>
     </row>
     <row r="39">
@@ -1292,7 +1280,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>28443.85059421328</v>
+        <v>20798.64219852273</v>
       </c>
     </row>
     <row r="42">
@@ -1355,7 +1343,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>12236.87858203007</v>
+        <v>15302.35101921223</v>
       </c>
     </row>
     <row r="45">
@@ -1418,7 +1406,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>10034.23439890405</v>
+        <v>23662.22159260079</v>
       </c>
     </row>
     <row r="48">
@@ -1460,7 +1448,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2508.558599726013</v>
+        <v>5915.555398150198</v>
       </c>
     </row>
     <row r="50">
@@ -1481,7 +1469,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>56444.27328698879</v>
+        <v>49686.47609053778</v>
       </c>
     </row>
     <row r="51">
@@ -1544,7 +1532,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>13278.82882686167</v>
+        <v>12939.97768740793</v>
       </c>
     </row>
     <row r="54">
